--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MONTANA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MONTANA_2021.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C35">
